--- a/Data for R/GES Sample Details.xlsx
+++ b/Data for R/GES Sample Details.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://cawater-my.sharepoint.com/personal/christina_burdi_water_ca_gov/Documents/Documents/Current Data/EDI Data Posting/Delta Smelt/R/Data for R/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://cawater-my.sharepoint.com/personal/christina_burdi_water_ca_gov/Documents/Documents/Current Data/EDI Data Posting/Delta Smelt/R/Delta Smelt Diet/Data for R/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="74" documentId="8_{00923493-3E5E-40A8-B99E-2A6292A41AC0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{AE0C02BC-8199-40FC-B262-1A59D090DA85}"/>
+  <xr:revisionPtr revIDLastSave="76" documentId="8_{00923493-3E5E-40A8-B99E-2A6292A41AC0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6B04C8D3-982D-49D8-85D3-842FB8FA8109}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{0AEA2967-1896-4425-B779-A0AFB1A8965B}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{0AEA2967-1896-4425-B779-A0AFB1A8965B}"/>
   </bookViews>
   <sheets>
     <sheet name="GES Samples" sheetId="1" r:id="rId1"/>
@@ -5266,6 +5266,9 @@
       <c r="A174">
         <v>2062</v>
       </c>
+      <c r="B174">
+        <v>317</v>
+      </c>
       <c r="C174" t="s">
         <v>2</v>
       </c>
@@ -5277,6 +5280,9 @@
       </c>
       <c r="F174">
         <v>1</v>
+      </c>
+      <c r="G174" s="6">
+        <v>0.60763888888888884</v>
       </c>
       <c r="H174"/>
       <c r="J174" s="1"/>

--- a/Data for R/GES Sample Details.xlsx
+++ b/Data for R/GES Sample Details.xlsx
@@ -1,20 +1,23 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://cawater-my.sharepoint.com/personal/christina_burdi_water_ca_gov/Documents/Documents/Current Data/EDI Data Posting/Delta Smelt/R/Delta Smelt Diet/Data for R/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="76" documentId="8_{00923493-3E5E-40A8-B99E-2A6292A41AC0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6B04C8D3-982D-49D8-85D3-842FB8FA8109}"/>
+  <xr:revisionPtr revIDLastSave="254" documentId="8_{00923493-3E5E-40A8-B99E-2A6292A41AC0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A1A3E503-6E04-45CD-97E3-6DA9A9EFB34A}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{0AEA2967-1896-4425-B779-A0AFB1A8965B}"/>
   </bookViews>
   <sheets>
     <sheet name="GES Samples" sheetId="1" r:id="rId1"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'GES Samples'!$A$1:$J$175</definedName>
+  </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -36,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="435" uniqueCount="43">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="610" uniqueCount="46">
   <si>
     <t>121-36-56.3</t>
   </si>
@@ -165,6 +168,15 @@
   </si>
   <si>
     <t>LogNumber</t>
+  </si>
+  <si>
+    <t>Error</t>
+  </si>
+  <si>
+    <t>Y</t>
+  </si>
+  <si>
+    <t>N</t>
   </si>
 </sst>
 </file>
@@ -566,16 +578,16 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{791958D3-FF9B-4623-B6E9-934E0593C7C8}">
   <dimension ref="A1:J175"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="2" max="2" width="13.28515625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="10.42578125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="11.28515625" customWidth="1"/>
-    <col min="8" max="8" width="15.140625" style="1" customWidth="1"/>
-    <col min="9" max="9" width="16.85546875" style="1" customWidth="1"/>
+    <col min="2" max="2" width="13.26953125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="10.453125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="11.26953125" customWidth="1"/>
+    <col min="8" max="8" width="15.1796875" style="1" customWidth="1"/>
+    <col min="9" max="9" width="16.81640625" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>42</v>
       </c>
@@ -603,8 +615,11 @@
       <c r="I1" s="5" t="s">
         <v>34</v>
       </c>
-    </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J1" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A2">
         <v>1889</v>
       </c>
@@ -632,8 +647,11 @@
       <c r="I2" s="3" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J2" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A3">
         <v>1890</v>
       </c>
@@ -661,8 +679,11 @@
       <c r="I3" s="3" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J3" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A4">
         <v>1891</v>
       </c>
@@ -690,8 +711,11 @@
       <c r="I4" s="3" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J4" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A5">
         <v>1892</v>
       </c>
@@ -719,8 +743,11 @@
       <c r="I5" s="3" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J5" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A6">
         <v>1893</v>
       </c>
@@ -748,8 +775,11 @@
       <c r="I6" s="3" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J6" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A7">
         <v>1894</v>
       </c>
@@ -777,8 +807,11 @@
       <c r="I7" s="3" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J7" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A8">
         <v>1895</v>
       </c>
@@ -806,8 +839,11 @@
       <c r="I8" s="3" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J8" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A9">
         <v>1896</v>
       </c>
@@ -835,8 +871,11 @@
       <c r="I9" s="3" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J9" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A10">
         <v>1897</v>
       </c>
@@ -864,8 +903,11 @@
       <c r="I10" s="3" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J10" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A11">
         <v>1898</v>
       </c>
@@ -893,8 +935,11 @@
       <c r="I11" s="3" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J11" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A12">
         <v>1899</v>
       </c>
@@ -922,8 +967,11 @@
       <c r="I12" s="3" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J12" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A13">
         <v>1900</v>
       </c>
@@ -951,8 +999,11 @@
       <c r="I13" s="3" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J13" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A14">
         <v>1901</v>
       </c>
@@ -980,8 +1031,11 @@
       <c r="I14" s="3" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J14" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A15">
         <v>1902</v>
       </c>
@@ -1009,8 +1063,11 @@
       <c r="I15" s="3" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J15" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A16">
         <v>1903</v>
       </c>
@@ -1038,8 +1095,11 @@
       <c r="I16" s="3" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J16" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="17" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A17">
         <v>1904</v>
       </c>
@@ -1067,8 +1127,11 @@
       <c r="I17" s="3" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="18" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J17" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="18" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A18">
         <v>1905</v>
       </c>
@@ -1096,8 +1159,11 @@
       <c r="I18" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="19" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J18" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="19" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A19">
         <v>1906</v>
       </c>
@@ -1125,8 +1191,11 @@
       <c r="I19" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="20" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J19" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="20" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A20">
         <v>1907</v>
       </c>
@@ -1154,8 +1223,11 @@
       <c r="I20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J20" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="21" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A21">
         <v>1908</v>
       </c>
@@ -1183,8 +1255,11 @@
       <c r="I21" s="3" t="s">
         <v>0</v>
       </c>
-    </row>
-    <row r="22" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J21" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="22" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A22">
         <v>1909</v>
       </c>
@@ -1204,8 +1279,11 @@
         <v>0.39583333333333331</v>
       </c>
       <c r="H22"/>
-    </row>
-    <row r="23" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J22" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="23" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A23">
         <v>1910</v>
       </c>
@@ -1225,8 +1303,11 @@
         <v>0.39583333333333331</v>
       </c>
       <c r="H23"/>
-    </row>
-    <row r="24" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J23" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="24" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A24">
         <v>1911</v>
       </c>
@@ -1246,8 +1327,11 @@
         <v>0.39583333333333331</v>
       </c>
       <c r="H24"/>
-    </row>
-    <row r="25" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J24" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="25" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A25">
         <v>1912</v>
       </c>
@@ -1267,8 +1351,11 @@
         <v>0.39583333333333331</v>
       </c>
       <c r="H25"/>
-    </row>
-    <row r="26" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J25" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="26" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A26">
         <v>1913</v>
       </c>
@@ -1288,8 +1375,11 @@
         <v>0.39583333333333331</v>
       </c>
       <c r="H26"/>
-    </row>
-    <row r="27" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J26" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="27" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A27">
         <v>1914</v>
       </c>
@@ -1309,8 +1399,11 @@
         <v>0.39583333333333331</v>
       </c>
       <c r="H27"/>
-    </row>
-    <row r="28" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J27" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="28" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A28">
         <v>1915</v>
       </c>
@@ -1330,8 +1423,11 @@
         <v>0.39583333333333331</v>
       </c>
       <c r="H28"/>
-    </row>
-    <row r="29" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J28" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="29" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A29">
         <v>1916</v>
       </c>
@@ -1351,8 +1447,11 @@
         <v>0.39583333333333331</v>
       </c>
       <c r="H29"/>
-    </row>
-    <row r="30" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J29" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="30" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A30">
         <v>1917</v>
       </c>
@@ -1372,8 +1471,11 @@
         <v>0.39583333333333331</v>
       </c>
       <c r="H30"/>
-    </row>
-    <row r="31" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J30" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="31" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A31">
         <v>1918</v>
       </c>
@@ -1393,8 +1495,11 @@
         <v>0.39583333333333331</v>
       </c>
       <c r="H31"/>
-    </row>
-    <row r="32" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J31" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="32" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A32">
         <v>1919</v>
       </c>
@@ -1414,8 +1519,11 @@
         <v>0.39583333333333331</v>
       </c>
       <c r="H32"/>
-    </row>
-    <row r="33" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J32" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="33" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A33">
         <v>1920</v>
       </c>
@@ -1435,8 +1543,11 @@
         <v>0.39583333333333331</v>
       </c>
       <c r="H33"/>
-    </row>
-    <row r="34" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J33" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="34" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A34">
         <v>1921</v>
       </c>
@@ -1456,8 +1567,11 @@
         <v>0.39583333333333331</v>
       </c>
       <c r="H34"/>
-    </row>
-    <row r="35" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J34" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="35" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A35">
         <v>1922</v>
       </c>
@@ -1477,8 +1591,11 @@
         <v>0.39583333333333331</v>
       </c>
       <c r="H35"/>
-    </row>
-    <row r="36" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J35" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="36" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A36">
         <v>1924</v>
       </c>
@@ -1498,8 +1615,11 @@
         <v>0.39583333333333331</v>
       </c>
       <c r="H36"/>
-    </row>
-    <row r="37" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J36" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="37" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A37">
         <v>1925</v>
       </c>
@@ -1519,8 +1639,11 @@
         <v>0.39583333333333331</v>
       </c>
       <c r="H37"/>
-    </row>
-    <row r="38" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J37" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="38" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A38">
         <v>1926</v>
       </c>
@@ -1540,8 +1663,11 @@
         <v>0.39583333333333331</v>
       </c>
       <c r="H38"/>
-    </row>
-    <row r="39" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J38" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="39" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A39">
         <v>1927</v>
       </c>
@@ -1561,8 +1687,11 @@
         <v>0.39583333333333331</v>
       </c>
       <c r="H39"/>
-    </row>
-    <row r="40" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J39" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="40" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A40">
         <v>1928</v>
       </c>
@@ -1590,8 +1719,11 @@
       <c r="I40" s="5" t="s">
         <v>32</v>
       </c>
-    </row>
-    <row r="41" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J40" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="41" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A41">
         <v>1929</v>
       </c>
@@ -1619,8 +1751,11 @@
       <c r="I41" s="5" t="s">
         <v>32</v>
       </c>
-    </row>
-    <row r="42" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J41" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="42" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A42">
         <v>1930</v>
       </c>
@@ -1648,8 +1783,11 @@
       <c r="I42" s="5" t="s">
         <v>32</v>
       </c>
-    </row>
-    <row r="43" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J42" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="43" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A43">
         <v>1931</v>
       </c>
@@ -1677,8 +1815,11 @@
       <c r="I43" s="5" t="s">
         <v>32</v>
       </c>
-    </row>
-    <row r="44" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J43" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="44" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A44">
         <v>1932</v>
       </c>
@@ -1706,8 +1847,11 @@
       <c r="I44" s="5" t="s">
         <v>32</v>
       </c>
-    </row>
-    <row r="45" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J44" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="45" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A45">
         <v>1933</v>
       </c>
@@ -1735,8 +1879,11 @@
       <c r="I45" s="5" t="s">
         <v>32</v>
       </c>
-    </row>
-    <row r="46" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J45" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="46" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A46">
         <v>1934</v>
       </c>
@@ -1764,8 +1911,11 @@
       <c r="I46" s="5" t="s">
         <v>32</v>
       </c>
-    </row>
-    <row r="47" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J46" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="47" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A47">
         <v>1935</v>
       </c>
@@ -1793,8 +1943,11 @@
       <c r="I47" s="5" t="s">
         <v>32</v>
       </c>
-    </row>
-    <row r="48" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J47" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="48" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A48">
         <v>1936</v>
       </c>
@@ -1822,8 +1975,11 @@
       <c r="I48" s="5" t="s">
         <v>32</v>
       </c>
-    </row>
-    <row r="49" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J48" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="49" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A49">
         <v>1937</v>
       </c>
@@ -1851,8 +2007,11 @@
       <c r="I49" s="5" t="s">
         <v>32</v>
       </c>
-    </row>
-    <row r="50" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J49" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="50" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A50">
         <v>1938</v>
       </c>
@@ -1880,8 +2039,11 @@
       <c r="I50" s="5" t="s">
         <v>32</v>
       </c>
-    </row>
-    <row r="51" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J50" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="51" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A51">
         <v>1939</v>
       </c>
@@ -1909,8 +2071,11 @@
       <c r="I51" s="5" t="s">
         <v>32</v>
       </c>
-    </row>
-    <row r="52" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J51" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="52" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A52">
         <v>1940</v>
       </c>
@@ -1938,8 +2103,11 @@
       <c r="I52" s="5" t="s">
         <v>32</v>
       </c>
-    </row>
-    <row r="53" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J52" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="53" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A53">
         <v>1941</v>
       </c>
@@ -1967,8 +2135,11 @@
       <c r="I53" s="5" t="s">
         <v>32</v>
       </c>
-    </row>
-    <row r="54" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J53" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="54" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A54">
         <v>1942</v>
       </c>
@@ -1996,8 +2167,11 @@
       <c r="I54" s="5" t="s">
         <v>32</v>
       </c>
-    </row>
-    <row r="55" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J54" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="55" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A55">
         <v>1943</v>
       </c>
@@ -2025,8 +2199,11 @@
       <c r="I55" s="5" t="s">
         <v>32</v>
       </c>
-    </row>
-    <row r="56" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J55" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="56" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A56">
         <v>1944</v>
       </c>
@@ -2054,8 +2231,11 @@
       <c r="I56" s="5" t="s">
         <v>32</v>
       </c>
-    </row>
-    <row r="57" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J56" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="57" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A57">
         <v>1945</v>
       </c>
@@ -2083,8 +2263,11 @@
       <c r="I57" s="5" t="s">
         <v>32</v>
       </c>
-    </row>
-    <row r="58" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J57" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="58" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A58">
         <v>1946</v>
       </c>
@@ -2112,8 +2295,11 @@
       <c r="I58" s="5" t="s">
         <v>32</v>
       </c>
-    </row>
-    <row r="59" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J58" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="59" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A59">
         <v>1947</v>
       </c>
@@ -2141,8 +2327,11 @@
       <c r="I59" s="5" t="s">
         <v>32</v>
       </c>
-    </row>
-    <row r="60" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J59" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="60" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A60">
         <v>1948</v>
       </c>
@@ -2170,8 +2359,11 @@
       <c r="I60" s="5" t="s">
         <v>32</v>
       </c>
-    </row>
-    <row r="61" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J60" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="61" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A61">
         <v>1949</v>
       </c>
@@ -2199,8 +2391,11 @@
       <c r="I61" s="5" t="s">
         <v>32</v>
       </c>
-    </row>
-    <row r="62" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J61" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="62" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A62">
         <v>1950</v>
       </c>
@@ -2228,8 +2423,11 @@
       <c r="I62" s="5" t="s">
         <v>32</v>
       </c>
-    </row>
-    <row r="63" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J62" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="63" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A63">
         <v>1951</v>
       </c>
@@ -2257,8 +2455,11 @@
       <c r="I63" s="5" t="s">
         <v>32</v>
       </c>
-    </row>
-    <row r="64" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J63" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="64" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A64">
         <v>1952</v>
       </c>
@@ -2286,8 +2487,11 @@
       <c r="I64" s="5" t="s">
         <v>32</v>
       </c>
-    </row>
-    <row r="65" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J64" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="65" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A65">
         <v>1953</v>
       </c>
@@ -2315,8 +2519,11 @@
       <c r="I65" s="5" t="s">
         <v>32</v>
       </c>
-    </row>
-    <row r="66" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J65" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="66" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A66">
         <v>1954</v>
       </c>
@@ -2344,8 +2551,11 @@
       <c r="I66" s="5" t="s">
         <v>32</v>
       </c>
-    </row>
-    <row r="67" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J66" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="67" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A67">
         <v>1955</v>
       </c>
@@ -2373,8 +2583,11 @@
       <c r="I67" s="5" t="s">
         <v>32</v>
       </c>
-    </row>
-    <row r="68" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J67" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="68" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A68">
         <v>1956</v>
       </c>
@@ -2402,8 +2615,11 @@
       <c r="I68" s="5" t="s">
         <v>32</v>
       </c>
-    </row>
-    <row r="69" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J68" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="69" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A69">
         <v>1957</v>
       </c>
@@ -2431,8 +2647,11 @@
       <c r="I69" s="3" t="s">
         <v>30</v>
       </c>
-    </row>
-    <row r="70" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J69" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="70" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A70">
         <v>1958</v>
       </c>
@@ -2460,8 +2679,11 @@
       <c r="I70" s="3" t="s">
         <v>30</v>
       </c>
-    </row>
-    <row r="71" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J70" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="71" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A71">
         <v>1959</v>
       </c>
@@ -2489,8 +2711,11 @@
       <c r="I71" s="3" t="s">
         <v>30</v>
       </c>
-    </row>
-    <row r="72" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J71" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="72" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A72">
         <v>1960</v>
       </c>
@@ -2518,8 +2743,11 @@
       <c r="I72" s="3" t="s">
         <v>30</v>
       </c>
-    </row>
-    <row r="73" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J72" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="73" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A73">
         <v>1961</v>
       </c>
@@ -2547,8 +2775,11 @@
       <c r="I73" s="3" t="s">
         <v>30</v>
       </c>
-    </row>
-    <row r="74" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J73" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="74" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A74">
         <v>1962</v>
       </c>
@@ -2576,8 +2807,11 @@
       <c r="I74" s="3" t="s">
         <v>30</v>
       </c>
-    </row>
-    <row r="75" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J74" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="75" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A75">
         <v>1963</v>
       </c>
@@ -2605,8 +2839,11 @@
       <c r="I75" s="3" t="s">
         <v>30</v>
       </c>
-    </row>
-    <row r="76" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J75" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="76" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A76">
         <v>1964</v>
       </c>
@@ -2634,8 +2871,11 @@
       <c r="I76" s="3" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="77" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J76" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="77" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A77">
         <v>1965</v>
       </c>
@@ -2663,8 +2903,11 @@
       <c r="I77" s="3" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="78" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J77" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="78" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A78">
         <v>1966</v>
       </c>
@@ -2692,8 +2935,11 @@
       <c r="I78" s="3" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="79" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J78" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="79" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A79">
         <v>1967</v>
       </c>
@@ -2721,8 +2967,11 @@
       <c r="I79" s="3" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="80" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J79" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="80" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A80">
         <v>1968</v>
       </c>
@@ -2750,8 +2999,11 @@
       <c r="I80" s="3" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="81" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="J80" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="81" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A81">
         <v>1969</v>
       </c>
@@ -2771,8 +3023,11 @@
         <v>0.66736111111111107</v>
       </c>
       <c r="H81"/>
-    </row>
-    <row r="82" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="J81" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="82" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A82">
         <v>1970</v>
       </c>
@@ -2792,8 +3047,11 @@
         <v>0.66736111111111107</v>
       </c>
       <c r="H82"/>
-    </row>
-    <row r="83" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="J82" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="83" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A83">
         <v>1971</v>
       </c>
@@ -2813,8 +3071,11 @@
         <v>0.66736111111111107</v>
       </c>
       <c r="H83"/>
-    </row>
-    <row r="84" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="J83" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="84" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A84">
         <v>1972</v>
       </c>
@@ -2834,8 +3095,11 @@
         <v>0.66736111111111107</v>
       </c>
       <c r="H84"/>
-    </row>
-    <row r="85" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="J84" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="85" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A85">
         <v>1973</v>
       </c>
@@ -2855,8 +3119,11 @@
         <v>0.66736111111111107</v>
       </c>
       <c r="H85"/>
-    </row>
-    <row r="86" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="J85" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="86" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A86">
         <v>1974</v>
       </c>
@@ -2876,8 +3143,11 @@
         <v>0.66736111111111107</v>
       </c>
       <c r="H86"/>
-    </row>
-    <row r="87" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="J86" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="87" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A87">
         <v>1975</v>
       </c>
@@ -2897,8 +3167,11 @@
         <v>0.66736111111111107</v>
       </c>
       <c r="H87"/>
-    </row>
-    <row r="88" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="J87" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="88" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A88">
         <v>1976</v>
       </c>
@@ -2918,8 +3191,11 @@
         <v>0.66736111111111107</v>
       </c>
       <c r="H88"/>
-    </row>
-    <row r="89" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="J88" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="89" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A89">
         <v>1977</v>
       </c>
@@ -2939,8 +3215,11 @@
         <v>0.66736111111111107</v>
       </c>
       <c r="H89"/>
-    </row>
-    <row r="90" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="J89" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="90" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A90">
         <v>1978</v>
       </c>
@@ -2960,8 +3239,11 @@
         <v>0.66736111111111107</v>
       </c>
       <c r="H90"/>
-    </row>
-    <row r="91" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="J90" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="91" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A91">
         <v>1979</v>
       </c>
@@ -2981,8 +3263,11 @@
         <v>0.66736111111111107</v>
       </c>
       <c r="H91"/>
-    </row>
-    <row r="92" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="J91" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="92" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A92">
         <v>1980</v>
       </c>
@@ -3002,8 +3287,11 @@
         <v>0.66736111111111107</v>
       </c>
       <c r="H92"/>
-    </row>
-    <row r="93" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="J92" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="93" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A93">
         <v>1981</v>
       </c>
@@ -3023,8 +3311,11 @@
         <v>0.66736111111111107</v>
       </c>
       <c r="H93"/>
-    </row>
-    <row r="94" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="J93" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="94" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A94">
         <v>1982</v>
       </c>
@@ -3044,8 +3335,11 @@
         <v>0.66736111111111107</v>
       </c>
       <c r="H94"/>
-    </row>
-    <row r="95" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="J94" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="95" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A95">
         <v>1983</v>
       </c>
@@ -3065,8 +3359,11 @@
         <v>0.66736111111111107</v>
       </c>
       <c r="H95"/>
-    </row>
-    <row r="96" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="J95" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="96" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A96">
         <v>1984</v>
       </c>
@@ -3086,8 +3383,11 @@
         <v>0.66736111111111107</v>
       </c>
       <c r="H96"/>
-    </row>
-    <row r="97" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J96" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="97" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A97">
         <v>1985</v>
       </c>
@@ -3107,8 +3407,11 @@
         <v>0.66736111111111107</v>
       </c>
       <c r="H97"/>
-    </row>
-    <row r="98" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J97" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="98" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A98">
         <v>1986</v>
       </c>
@@ -3128,8 +3431,11 @@
         <v>0.66736111111111107</v>
       </c>
       <c r="H98"/>
-    </row>
-    <row r="99" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J98" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="99" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A99">
         <v>1987</v>
       </c>
@@ -3149,8 +3455,11 @@
         <v>0.66736111111111107</v>
       </c>
       <c r="H99"/>
-    </row>
-    <row r="100" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J99" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="100" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A100">
         <v>1988</v>
       </c>
@@ -3170,8 +3479,11 @@
         <v>0.66736111111111107</v>
       </c>
       <c r="H100"/>
-    </row>
-    <row r="101" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J100" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="101" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A101">
         <v>1989</v>
       </c>
@@ -3191,8 +3503,11 @@
         <v>0.66736111111111107</v>
       </c>
       <c r="H101"/>
-    </row>
-    <row r="102" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J101" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="102" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A102">
         <v>1990</v>
       </c>
@@ -3212,8 +3527,11 @@
         <v>0.66736111111111107</v>
       </c>
       <c r="H102"/>
-    </row>
-    <row r="103" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J102" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="103" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A103">
         <v>1991</v>
       </c>
@@ -3233,8 +3551,11 @@
         <v>0.66736111111111107</v>
       </c>
       <c r="H103"/>
-    </row>
-    <row r="104" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J103" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="104" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A104">
         <v>1992</v>
       </c>
@@ -3254,8 +3575,11 @@
         <v>0.66736111111111107</v>
       </c>
       <c r="H104"/>
-    </row>
-    <row r="105" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J104" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="105" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A105">
         <v>1993</v>
       </c>
@@ -3275,8 +3599,11 @@
         <v>0.66736111111111107</v>
       </c>
       <c r="H105"/>
-    </row>
-    <row r="106" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J105" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="106" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A106">
         <v>1994</v>
       </c>
@@ -3296,8 +3623,11 @@
         <v>0.66736111111111107</v>
       </c>
       <c r="H106"/>
-    </row>
-    <row r="107" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J106" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="107" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A107">
         <v>1995</v>
       </c>
@@ -3317,8 +3647,11 @@
         <v>0.66736111111111107</v>
       </c>
       <c r="H107"/>
-    </row>
-    <row r="108" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J107" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="108" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A108">
         <v>1996</v>
       </c>
@@ -3338,8 +3671,11 @@
         <v>0.66736111111111107</v>
       </c>
       <c r="H108"/>
-    </row>
-    <row r="109" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J108" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="109" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A109">
         <v>1997</v>
       </c>
@@ -3359,8 +3695,11 @@
         <v>0.66736111111111107</v>
       </c>
       <c r="H109"/>
-    </row>
-    <row r="110" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J109" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="110" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A110">
         <v>1998</v>
       </c>
@@ -3388,8 +3727,11 @@
       <c r="I110" s="3" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="111" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J110" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="111" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A111">
         <v>1999</v>
       </c>
@@ -3417,8 +3759,11 @@
       <c r="I111" s="3" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="112" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J111" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="112" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A112">
         <v>2000</v>
       </c>
@@ -3446,8 +3791,11 @@
       <c r="I112" s="3" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="113" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J112" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="113" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A113">
         <v>2001</v>
       </c>
@@ -3475,8 +3823,11 @@
       <c r="I113" s="3" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="114" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J113" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="114" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A114">
         <v>2002</v>
       </c>
@@ -3504,8 +3855,11 @@
       <c r="I114" s="3" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="115" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J114" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="115" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A115">
         <v>2003</v>
       </c>
@@ -3533,8 +3887,11 @@
       <c r="I115" s="3" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="116" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J115" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="116" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A116">
         <v>2004</v>
       </c>
@@ -3562,8 +3919,11 @@
       <c r="I116" s="3" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="117" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J116" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="117" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A117">
         <v>2005</v>
       </c>
@@ -3591,8 +3951,11 @@
       <c r="I117" s="3" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="118" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J117" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="118" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A118">
         <v>2006</v>
       </c>
@@ -3620,8 +3983,11 @@
       <c r="I118" s="3" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="119" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J118" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="119" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A119">
         <v>2007</v>
       </c>
@@ -3649,8 +4015,11 @@
       <c r="I119" s="3" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="120" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J119" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="120" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A120">
         <v>2008</v>
       </c>
@@ -3678,8 +4047,11 @@
       <c r="I120" s="3" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="121" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J120" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="121" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A121">
         <v>2009</v>
       </c>
@@ -3707,8 +4079,11 @@
       <c r="I121" s="3" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="122" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J121" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="122" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A122">
         <v>2010</v>
       </c>
@@ -3736,8 +4111,11 @@
       <c r="I122" s="3" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="123" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J122" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="123" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A123">
         <v>2011</v>
       </c>
@@ -3765,8 +4143,11 @@
       <c r="I123" s="3" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="124" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J123" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="124" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A124">
         <v>2012</v>
       </c>
@@ -3794,8 +4175,11 @@
       <c r="I124" s="3" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="125" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J124" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="125" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A125">
         <v>2013</v>
       </c>
@@ -3823,8 +4207,11 @@
       <c r="I125" s="3" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="126" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J125" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="126" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A126">
         <v>2014</v>
       </c>
@@ -3852,8 +4239,11 @@
       <c r="I126" s="3" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="127" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J126" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="127" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A127">
         <v>2015</v>
       </c>
@@ -3881,8 +4271,11 @@
       <c r="I127" s="3" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="128" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J127" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="128" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A128">
         <v>2016</v>
       </c>
@@ -3910,9 +4303,11 @@
       <c r="I128" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="J128" s="1"/>
-    </row>
-    <row r="129" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J128" s="1" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="129" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A129">
         <v>2017</v>
       </c>
@@ -3940,9 +4335,11 @@
       <c r="I129" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="J129" s="1"/>
-    </row>
-    <row r="130" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J129" s="1" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="130" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A130">
         <v>2018</v>
       </c>
@@ -3970,9 +4367,11 @@
       <c r="I130" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="J130" s="1"/>
-    </row>
-    <row r="131" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J130" s="1" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="131" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A131">
         <v>2019</v>
       </c>
@@ -4000,9 +4399,11 @@
       <c r="I131" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="J131" s="1"/>
-    </row>
-    <row r="132" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J131" s="1" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="132" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A132">
         <v>2020</v>
       </c>
@@ -4030,9 +4431,11 @@
       <c r="I132" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="J132" s="1"/>
-    </row>
-    <row r="133" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J132" s="1" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="133" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A133">
         <v>2021</v>
       </c>
@@ -4060,9 +4463,11 @@
       <c r="I133" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="J133" s="1"/>
-    </row>
-    <row r="134" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J133" s="1" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="134" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A134">
         <v>2022</v>
       </c>
@@ -4090,9 +4495,11 @@
       <c r="I134" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="J134" s="1"/>
-    </row>
-    <row r="135" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J134" s="1" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="135" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A135">
         <v>2023</v>
       </c>
@@ -4120,9 +4527,11 @@
       <c r="I135" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="J135" s="1"/>
-    </row>
-    <row r="136" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J135" s="1" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="136" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A136">
         <v>2024</v>
       </c>
@@ -4150,9 +4559,11 @@
       <c r="I136" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="J136" s="1"/>
-    </row>
-    <row r="137" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J136" s="1" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="137" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A137">
         <v>2025</v>
       </c>
@@ -4180,9 +4591,11 @@
       <c r="I137" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="J137" s="1"/>
-    </row>
-    <row r="138" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J137" s="1" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="138" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A138">
         <v>2026</v>
       </c>
@@ -4210,9 +4623,11 @@
       <c r="I138" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="J138" s="1"/>
-    </row>
-    <row r="139" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J138" s="1" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="139" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A139">
         <v>2027</v>
       </c>
@@ -4240,9 +4655,11 @@
       <c r="I139" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="J139" s="1"/>
-    </row>
-    <row r="140" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J139" s="1" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="140" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A140">
         <v>2028</v>
       </c>
@@ -4270,9 +4687,11 @@
       <c r="I140" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="J140" s="1"/>
-    </row>
-    <row r="141" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J140" s="1" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="141" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A141">
         <v>2029</v>
       </c>
@@ -4300,9 +4719,11 @@
       <c r="I141" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="J141" s="1"/>
-    </row>
-    <row r="142" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J141" s="1" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="142" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A142">
         <v>2030</v>
       </c>
@@ -4330,9 +4751,11 @@
       <c r="I142" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="J142" s="1"/>
-    </row>
-    <row r="143" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J142" s="1" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="143" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A143">
         <v>2031</v>
       </c>
@@ -4360,9 +4783,11 @@
       <c r="I143" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="J143" s="1"/>
-    </row>
-    <row r="144" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J143" s="1" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="144" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A144">
         <v>2032</v>
       </c>
@@ -4390,9 +4815,11 @@
       <c r="I144" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="J144" s="1"/>
-    </row>
-    <row r="145" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J144" s="1" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="145" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A145">
         <v>2033</v>
       </c>
@@ -4420,9 +4847,11 @@
       <c r="I145" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="J145" s="1"/>
-    </row>
-    <row r="146" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J145" s="1" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="146" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A146">
         <v>2034</v>
       </c>
@@ -4450,9 +4879,11 @@
       <c r="I146" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="J146" s="1"/>
-    </row>
-    <row r="147" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J146" s="1" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="147" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A147">
         <v>2035</v>
       </c>
@@ -4480,9 +4911,11 @@
       <c r="I147" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="J147" s="1"/>
-    </row>
-    <row r="148" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J147" s="1" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="148" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A148">
         <v>2036</v>
       </c>
@@ -4510,9 +4943,11 @@
       <c r="I148" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="J148" s="1"/>
-    </row>
-    <row r="149" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J148" s="1" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="149" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A149">
         <v>2037</v>
       </c>
@@ -4540,9 +4975,11 @@
       <c r="I149" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="J149" s="1"/>
-    </row>
-    <row r="150" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J149" s="1" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="150" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A150">
         <v>2038</v>
       </c>
@@ -4570,9 +5007,11 @@
       <c r="I150" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="J150" s="1"/>
-    </row>
-    <row r="151" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J150" s="1" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="151" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A151">
         <v>2039</v>
       </c>
@@ -4600,9 +5039,11 @@
       <c r="I151" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="J151" s="1"/>
-    </row>
-    <row r="152" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J151" s="1" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="152" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A152">
         <v>2040</v>
       </c>
@@ -4630,9 +5071,11 @@
       <c r="I152" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="J152" s="1"/>
-    </row>
-    <row r="153" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J152" s="1" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="153" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A153">
         <v>2041</v>
       </c>
@@ -4660,9 +5103,11 @@
       <c r="I153" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="J153" s="1"/>
-    </row>
-    <row r="154" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J153" s="1" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="154" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A154">
         <v>2042</v>
       </c>
@@ -4690,9 +5135,11 @@
       <c r="I154" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="J154" s="1"/>
-    </row>
-    <row r="155" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J154" s="1" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="155" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A155">
         <v>2043</v>
       </c>
@@ -4720,9 +5167,11 @@
       <c r="I155" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="J155" s="1"/>
-    </row>
-    <row r="156" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J155" s="1" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="156" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A156">
         <v>2044</v>
       </c>
@@ -4750,9 +5199,11 @@
       <c r="I156" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="J156" s="1"/>
-    </row>
-    <row r="157" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J156" s="1" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="157" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A157">
         <v>2045</v>
       </c>
@@ -4780,9 +5231,11 @@
       <c r="I157" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="J157" s="1"/>
-    </row>
-    <row r="158" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J157" s="1" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="158" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A158">
         <v>2046</v>
       </c>
@@ -4810,9 +5263,11 @@
       <c r="I158" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="J158" s="1"/>
-    </row>
-    <row r="159" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J158" s="1" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="159" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A159">
         <v>2047</v>
       </c>
@@ -4840,9 +5295,11 @@
       <c r="I159" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="J159" s="1"/>
-    </row>
-    <row r="160" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J159" s="1" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="160" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A160">
         <v>2048</v>
       </c>
@@ -4870,9 +5327,11 @@
       <c r="I160" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="J160" s="1"/>
-    </row>
-    <row r="161" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J160" s="1" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="161" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A161">
         <v>2049</v>
       </c>
@@ -4900,9 +5359,11 @@
       <c r="I161" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="J161" s="1"/>
-    </row>
-    <row r="162" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J161" s="1" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="162" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A162">
         <v>2050</v>
       </c>
@@ -4930,9 +5391,11 @@
       <c r="I162" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="J162" s="1"/>
-    </row>
-    <row r="163" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J162" s="1" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="163" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A163">
         <v>2051</v>
       </c>
@@ -4960,9 +5423,11 @@
       <c r="I163" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="J163" s="1"/>
-    </row>
-    <row r="164" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J163" s="1" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="164" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A164">
         <v>2052</v>
       </c>
@@ -4990,9 +5455,11 @@
       <c r="I164" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="J164" s="1"/>
-    </row>
-    <row r="165" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J164" s="1" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="165" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A165">
         <v>2053</v>
       </c>
@@ -5020,9 +5487,11 @@
       <c r="I165" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="J165" s="1"/>
-    </row>
-    <row r="166" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J165" s="1" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="166" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A166">
         <v>2054</v>
       </c>
@@ -5050,9 +5519,11 @@
       <c r="I166" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="J166" s="1"/>
-    </row>
-    <row r="167" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J166" s="1" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="167" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A167">
         <v>2055</v>
       </c>
@@ -5080,9 +5551,11 @@
       <c r="I167" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="J167" s="1"/>
-    </row>
-    <row r="168" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J167" s="1" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="168" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A168">
         <v>2056</v>
       </c>
@@ -5110,9 +5583,11 @@
       <c r="I168" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="J168" s="1"/>
-    </row>
-    <row r="169" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J168" s="1" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="169" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A169">
         <v>2057</v>
       </c>
@@ -5140,9 +5615,11 @@
       <c r="I169" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="J169" s="1"/>
-    </row>
-    <row r="170" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J169" s="1" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="170" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A170">
         <v>2058</v>
       </c>
@@ -5170,9 +5647,11 @@
       <c r="I170" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="J170" s="1"/>
-    </row>
-    <row r="171" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J170" s="1" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="171" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A171">
         <v>2059</v>
       </c>
@@ -5200,9 +5679,11 @@
       <c r="I171" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="J171" s="1"/>
-    </row>
-    <row r="172" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J171" s="1" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="172" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A172">
         <v>2060</v>
       </c>
@@ -5230,9 +5711,11 @@
       <c r="I172" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="J172" s="1"/>
-    </row>
-    <row r="173" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J172" s="1" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="173" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A173">
         <v>2061</v>
       </c>
@@ -5260,9 +5743,11 @@
       <c r="I173" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="J173" s="1"/>
-    </row>
-    <row r="174" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J173" s="1" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="174" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A174">
         <v>2062</v>
       </c>
@@ -5285,9 +5770,11 @@
         <v>0.60763888888888884</v>
       </c>
       <c r="H174"/>
-      <c r="J174" s="1"/>
-    </row>
-    <row r="175" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J174" s="1" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="175" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A175">
         <v>2063</v>
       </c>
@@ -5315,9 +5802,12 @@
       <c r="I175" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="J175" s="1"/>
+      <c r="J175" s="1" t="s">
+        <v>45</v>
+      </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:J175" xr:uid="{791958D3-FF9B-4623-B6E9-934E0593C7C8}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:I175">
     <sortCondition ref="A112:A175"/>
   </sortState>
